--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260625.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260625.xlsx
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,350,000</t>
+          <t>5,859,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5,859,000</t>
+          <t>7,350,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>豐興</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,201,000</t>
+          <t>9,024,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>豐興</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>9,024,000</t>
+          <t>2,201,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
